--- a/docs/Shopee_mass_upload_FILLED_category_100642.xlsx
+++ b/docs/Shopee_mass_upload_FILLED_category_100642.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{274D92B5-6FB9-4880-81FB-DBBC921EF7EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8197C1A3-1FF1-4754-B44C-78A0B0C39A5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1882" uniqueCount="621">
   <si>
     <t>Tentang Template Mass Upload</t>
   </si>
@@ -1902,9 +1902,6 @@
     <t>VND-MSTR-ALL</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/adrian-dev-art/vendoraman/main/docs/shopee_assets/cover_master_bundle.jpg</t>
   </si>
   <si>
@@ -1921,9 +1918,6 @@
   </si>
   <si>
     <t>https://raw.githubusercontent.com/adrian-dev-art/vendoraman/main/docs/shopee_assets/cover_corporate.jpg</t>
-  </si>
-  <si>
-    <t>Tidak Ada Merek</t>
   </si>
   <si>
     <t>Template Excel Wedding Planner &amp; Rundown Resepsi Pernikahan Hari-H + Kalkulator Porsi Katering</t>
@@ -4189,7 +4183,7 @@
         <v>593</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>594</v>
+        <v>220</v>
       </c>
       <c r="Q7" s="2">
         <v>149000</v>
@@ -4198,22 +4192,22 @@
         <v>999</v>
       </c>
       <c r="W7" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="X7" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="X7" s="2" t="s">
+      <c r="Y7" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="Y7" s="2" t="s">
+      <c r="Z7" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="Z7" s="2" t="s">
+      <c r="AA7" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="AA7" s="2" t="s">
+      <c r="AB7" s="2" t="s">
         <v>599</v>
-      </c>
-      <c r="AB7" s="2" t="s">
-        <v>600</v>
       </c>
       <c r="AF7" s="2">
         <v>10</v>
@@ -4229,9 +4223,6 @@
       </c>
       <c r="AJ7" s="2" t="s">
         <v>326</v>
-      </c>
-      <c r="AL7" s="1" t="s">
-        <v>601</v>
       </c>
       <c r="BE7" s="2" t="s">
         <v>467</v>
@@ -4242,16 +4233,16 @@
         <v>101514</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>604</v>
-      </c>
       <c r="J8" s="2" t="s">
-        <v>594</v>
+        <v>220</v>
       </c>
       <c r="Q8" s="2">
         <v>69000</v>
@@ -4260,19 +4251,19 @@
         <v>999</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="X8" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="Y8" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="Y8" s="2" t="s">
+      <c r="Z8" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="Z8" s="2" t="s">
-        <v>598</v>
-      </c>
       <c r="AA8" s="2" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AF8" s="2">
         <v>10</v>
@@ -4288,9 +4279,6 @@
       </c>
       <c r="AJ8" s="2" t="s">
         <v>326</v>
-      </c>
-      <c r="AL8" s="1" t="s">
-        <v>601</v>
       </c>
       <c r="BE8" s="2" t="s">
         <v>467</v>
@@ -4301,16 +4289,16 @@
         <v>101514</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>605</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>607</v>
-      </c>
       <c r="J9" s="2" t="s">
-        <v>594</v>
+        <v>220</v>
       </c>
       <c r="Q9" s="2">
         <v>59000</v>
@@ -4319,19 +4307,19 @@
         <v>999</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="X9" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="Y9" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="Y9" s="2" t="s">
+      <c r="Z9" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="Z9" s="2" t="s">
-        <v>598</v>
-      </c>
       <c r="AA9" s="2" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AF9" s="2">
         <v>10</v>
@@ -4347,9 +4335,6 @@
       </c>
       <c r="AJ9" s="2" t="s">
         <v>326</v>
-      </c>
-      <c r="AL9" s="1" t="s">
-        <v>601</v>
       </c>
       <c r="BE9" s="2" t="s">
         <v>467</v>
@@ -4360,16 +4345,16 @@
         <v>101514</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>610</v>
-      </c>
       <c r="J10" s="2" t="s">
-        <v>594</v>
+        <v>220</v>
       </c>
       <c r="Q10" s="2">
         <v>49000</v>
@@ -4378,16 +4363,16 @@
         <v>999</v>
       </c>
       <c r="W10" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="X10" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="X10" s="2" t="s">
+      <c r="Y10" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="Y10" s="2" t="s">
+      <c r="Z10" s="2" t="s">
         <v>597</v>
-      </c>
-      <c r="Z10" s="2" t="s">
-        <v>598</v>
       </c>
       <c r="AF10" s="2">
         <v>10</v>
@@ -4403,9 +4388,6 @@
       </c>
       <c r="AJ10" s="2" t="s">
         <v>326</v>
-      </c>
-      <c r="AL10" s="1" t="s">
-        <v>601</v>
       </c>
       <c r="BE10" s="2" t="s">
         <v>467</v>
@@ -4416,16 +4398,16 @@
         <v>101514</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>613</v>
-      </c>
       <c r="J11" s="2" t="s">
-        <v>594</v>
+        <v>220</v>
       </c>
       <c r="Q11" s="2">
         <v>49000</v>
@@ -4434,13 +4416,13 @@
         <v>999</v>
       </c>
       <c r="W11" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="X11" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="X11" s="2" t="s">
-        <v>596</v>
-      </c>
       <c r="Y11" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AF11" s="2">
         <v>10</v>
@@ -4456,9 +4438,6 @@
       </c>
       <c r="AJ11" s="2" t="s">
         <v>326</v>
-      </c>
-      <c r="AL11" s="1" t="s">
-        <v>601</v>
       </c>
       <c r="BE11" s="2" t="s">
         <v>467</v>
@@ -4469,16 +4448,16 @@
         <v>101514</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>616</v>
-      </c>
       <c r="J12" s="2" t="s">
-        <v>594</v>
+        <v>220</v>
       </c>
       <c r="Q12" s="2">
         <v>49000</v>
@@ -4487,13 +4466,13 @@
         <v>999</v>
       </c>
       <c r="W12" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="X12" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="X12" s="2" t="s">
-        <v>596</v>
-      </c>
       <c r="Y12" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AF12" s="2">
         <v>10</v>
@@ -4509,9 +4488,6 @@
       </c>
       <c r="AJ12" s="2" t="s">
         <v>326</v>
-      </c>
-      <c r="AL12" s="1" t="s">
-        <v>601</v>
       </c>
       <c r="BE12" s="2" t="s">
         <v>467</v>
@@ -4522,16 +4498,16 @@
         <v>101514</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>619</v>
-      </c>
       <c r="J13" s="2" t="s">
-        <v>594</v>
+        <v>220</v>
       </c>
       <c r="Q13" s="2">
         <v>49000</v>
@@ -4540,13 +4516,13 @@
         <v>999</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="Y13" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AF13" s="2">
         <v>10</v>
@@ -4562,9 +4538,6 @@
       </c>
       <c r="AJ13" s="2" t="s">
         <v>326</v>
-      </c>
-      <c r="AL13" s="1" t="s">
-        <v>601</v>
       </c>
       <c r="BE13" s="2" t="s">
         <v>467</v>
@@ -4575,16 +4548,16 @@
         <v>101514</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>620</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>622</v>
-      </c>
       <c r="J14" s="2" t="s">
-        <v>594</v>
+        <v>220</v>
       </c>
       <c r="Q14" s="2">
         <v>99000</v>
@@ -4593,13 +4566,13 @@
         <v>999</v>
       </c>
       <c r="W14" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="X14" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="Y14" s="2" t="s">
         <v>595</v>
-      </c>
-      <c r="X14" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="Y14" s="2" t="s">
-        <v>596</v>
       </c>
       <c r="AF14" s="2">
         <v>10</v>
@@ -4615,9 +4588,6 @@
       </c>
       <c r="AJ14" s="2" t="s">
         <v>326</v>
-      </c>
-      <c r="AL14" s="1" t="s">
-        <v>601</v>
       </c>
       <c r="BE14" s="2" t="s">
         <v>467</v>
